--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20211.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>FRIAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>OMAR</t>
   </si>
 </sst>
 </file>
@@ -483,10 +501,10 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>31</v>
@@ -495,7 +513,7 @@
         <v>77.5</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -535,19 +553,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>88.37</v>
+        <v>93.02</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -561,10 +579,10 @@
         <v>22</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>3</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>19</v>
@@ -573,7 +591,7 @@
         <v>86.36</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -587,10 +605,10 @@
         <v>38</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>6</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
       </c>
       <c r="F6">
         <v>32</v>
@@ -599,7 +617,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -678,16 +696,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>77.5</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -701,16 +722,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.45</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -724,16 +748,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>93.02</v>
+      </c>
+      <c r="H4">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -747,16 +774,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>81.81999999999999</v>
+      </c>
+      <c r="H5">
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -770,16 +800,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -855,10 +888,10 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>31</v>
@@ -907,19 +940,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>88.37</v>
+        <v>93.02</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -933,19 +966,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>86.36</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -959,19 +992,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G6">
-        <v>84.20999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1007,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1037,6 +1070,52 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920009</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920013</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20211.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20211.xlsx
@@ -631,19 +631,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>80</v>
+        <v>82.86</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -826,16 +826,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H7">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -1018,19 +1021,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>80</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20211.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,24 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>FRIAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>OMAR</t>
   </si>
 </sst>
 </file>
@@ -631,10 +613,10 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>29</v>
@@ -643,7 +625,7 @@
         <v>82.86</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -826,19 +808,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>85.70999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -894,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -920,16 +902,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G3">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -946,13 +928,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>93.02</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>8.699999999999999</v>
@@ -972,16 +954,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>81.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -998,13 +980,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>78.95</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>7.9</v>
@@ -1021,19 +1003,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1073,52 +1055,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920009</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920013</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
